--- a/output/results.xlsx
+++ b/output/results.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="UAV Events" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Waypoint Updates" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Summary Metrics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Waypoints" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="UAV Metrics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Summary Metrics" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +437,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>waypoint_id</t>
+          <t>wp_id</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -487,7 +488,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -526,13 +527,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>17.5</v>
+        <v>36</v>
       </c>
       <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -571,13 +572,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6.08276253029822</v>
+        <v>12.16552506059644</v>
       </c>
       <c r="B4" t="n">
         <v>2</v>
@@ -616,13 +617,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>13.91723746970178</v>
+        <v>28.83447493940356</v>
       </c>
       <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
@@ -633,13 +634,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>448.9299082816925</v>
+        <v>515.2593816132376</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -647,7 +648,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -661,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>12.5</v>
+        <v>26</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -671,7 +672,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
@@ -682,13 +683,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
-        <v>334.820610868813</v>
+        <v>327.9763458157603</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -696,7 +697,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -710,7 +711,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -720,7 +721,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>10.5</v>
+        <v>21</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -734,7 +735,7 @@
         <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>515.2593816132376</v>
+        <v>359.9985069829038</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -745,7 +746,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -753,19 +754,19 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>964.18928989493</v>
+        <v>808.9284152645962</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>9.5</v>
+        <v>20</v>
       </c>
       <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>11.08276253029822</v>
+        <v>22.16552506059644</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
@@ -779,42 +780,42 @@
         <v>37</v>
       </c>
       <c r="E8" t="n">
+        <v>292.9497807222561</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>114.1270985852852</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>114.1270985852852</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
-        <v>8.91723746970178</v>
+        <v>18.83447493940356</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>continue</t>
+          <t>backup</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>12.30116263352131</v>
+        <v>24.60232526704263</v>
       </c>
       <c r="B9" t="n">
         <v>0</v>
@@ -828,10 +829,10 @@
         <v>19</v>
       </c>
       <c r="E9" t="n">
-        <v>327.9763458157603</v>
+        <v>452.9450791042515</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -839,7 +840,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -847,19 +848,19 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>662.7969566845734</v>
+        <v>787.7656899730645</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>7.698837366478687</v>
+        <v>16.39767473295737</v>
       </c>
       <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>15.5</v>
+        <v>31</v>
       </c>
       <c r="B10" t="n">
         <v>1</v>
@@ -873,7 +874,7 @@
         <v>60</v>
       </c>
       <c r="E10" t="n">
-        <v>515.2593816132376</v>
+        <v>359.9985069829038</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -884,7 +885,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -892,23 +893,23 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>964.18928989493</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>808.9284152645962</v>
       </c>
       <c r="L10" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>continue</t>
+          <t>backup</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>17.16552506059644</v>
+        <v>34.33105012119288</v>
       </c>
       <c r="B11" t="n">
         <v>2</v>
@@ -922,38 +923,38 @@
         <v>37</v>
       </c>
       <c r="E11" t="n">
+        <v>292.9497807222561</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>114.1270985852852</v>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>114.1270985852852</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" t="n">
-        <v>2.83447493940356</v>
+        <v>6.668949878807119</v>
       </c>
       <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>17.30116263352132</v>
+        <v>34.60232526704263</v>
       </c>
       <c r="B12" t="n">
         <v>0</v>
@@ -967,10 +968,10 @@
         <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>327.9763458157603</v>
+        <v>452.9450791042515</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -978,7 +979,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -986,40 +987,40 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>662.7969566845734</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>787.7656899730645</v>
       </c>
       <c r="L12" t="n">
-        <v>2.698837366478685</v>
+        <v>6.39767473295737</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>continue</t>
+          <t>backup</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20.42442890089805</v>
+        <v>40.8488578017961</v>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>crash</t>
+          <t>depot_arrival</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>60</v>
       </c>
       <c r="E13" t="n">
-        <v>146.1529120578085</v>
+        <v>370.8752724862744</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1027,7 +1028,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1035,19 +1036,19 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>964.18928989493</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>808.9284152645962</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.4244289008980502</v>
+        <v>0.1511421982038996</v>
       </c>
       <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>20.83669653945405</v>
+        <v>41.67339307890811</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
@@ -1061,10 +1062,10 @@
         <v>19</v>
       </c>
       <c r="E14" t="n">
-        <v>104.0104123984499</v>
+        <v>150.4403927080818</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1072,7 +1073,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1080,36 +1081,36 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>662.7969566845734</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>787.7656899730645</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.8366965394540529</v>
+        <v>-0.6733930789081057</v>
       </c>
       <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>22.92442890089805</v>
+        <v>45.8488578017961</v>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>crash</t>
+          <t>arrival</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>54</v>
       </c>
       <c r="E15" t="n">
-        <v>125.2050337119815</v>
+        <v>499.7524037865747</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1125,19 +1126,19 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>499.7524037865747</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.92442890089805</v>
+        <v>36</v>
       </c>
       <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>23.24828759089466</v>
+        <v>46.49657518178932</v>
       </c>
       <c r="B16" t="n">
         <v>2</v>
@@ -1151,10 +1152,10 @@
         <v>37</v>
       </c>
       <c r="E16" t="n">
-        <v>587.9826663713962</v>
+        <v>458.7130105615833</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1170,19 +1171,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>587.9826663713962</v>
+        <v>458.7130105615833</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>13.91723746970178</v>
+        <v>28.83447493940356</v>
       </c>
       <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>23.83669653945405</v>
+        <v>47.67339307890811</v>
       </c>
       <c r="B17" t="n">
         <v>0</v>
@@ -1196,10 +1197,10 @@
         <v>77</v>
       </c>
       <c r="E17" t="n">
-        <v>120.4397153328737</v>
+        <v>367.0019058214374</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1221,16 +1222,16 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-3.836696539454053</v>
+        <v>-6.673393078908106</v>
       </c>
       <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>25.42442890089805</v>
+        <v>53.67339307890811</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1238,10 +1239,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="E18" t="n">
-        <v>125.2050337119815</v>
+        <v>367.0019058214374</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -1266,30 +1267,30 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-5.42442890089805</v>
+        <v>-12.67339307890811</v>
       </c>
       <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>26.83669653945405</v>
+        <v>55.8488578017961</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>crash</t>
+          <t>departure</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>120.4397153328737</v>
+        <v>370.8752724862744</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1297,7 +1298,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1305,44 +1306,48 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>499.7524037865747</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-6.836696539454053</v>
-      </c>
-      <c r="M19" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>continue</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>27.92442890089805</v>
+        <v>56.49657518178932</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>crash</t>
+          <t>departure</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="E20" t="n">
-        <v>125.2050337119815</v>
+        <v>458.7130105615833</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1353,41 +1358,45 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>458.7130105615833</v>
       </c>
       <c r="L20" t="n">
-        <v>-7.92442890089805</v>
-      </c>
-      <c r="M20" t="inlineStr"/>
+        <v>18.83447493940356</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>backup</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>28.24828759089466</v>
+        <v>59.67339307890811</v>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>departure</t>
+          <t>crash</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="E21" t="n">
-        <v>587.9826663713962</v>
+        <v>367.0019058214374</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>good</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1395,40 +1404,36 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>587.9826663713962</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>8.917237469701778</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>backup</t>
-        </is>
-      </c>
+        <v>-18.67339307890811</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>29.83669653945405</v>
+        <v>61.8488578017961</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>crash</t>
+          <t>arrival</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>120.4397153328737</v>
+        <v>436.1844374061087</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1436,7 +1441,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1444,22 +1449,22 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>935.9368411926835</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>-9.836696539454053</v>
+        <v>20</v>
       </c>
       <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>30.42442890089805</v>
+        <v>65.67339307890811</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1467,10 +1472,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="E23" t="n">
-        <v>125.2050337119815</v>
+        <v>216.2341291490647</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -1495,38 +1500,38 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>-10.42442890089805</v>
+        <v>-24.67339307890811</v>
       </c>
       <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>32.83669653945405</v>
+        <v>68.66210024238576</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>crash</t>
+          <t>depot_arrival</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="E24" t="n">
-        <v>120.4397153328737</v>
+        <v>514.330148794661</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1537,19 +1542,19 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>458.7130105615833</v>
       </c>
       <c r="L24" t="n">
-        <v>-12.83669653945405</v>
+        <v>6.668949878807119</v>
       </c>
       <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>32.92442890089805</v>
+        <v>71.67339307890811</v>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1557,10 +1562,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="E25" t="n">
-        <v>125.2050337119815</v>
+        <v>216.2341291490647</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -1585,30 +1590,30 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>-12.92442890089805</v>
+        <v>-30.67339307890811</v>
       </c>
       <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>34.33105012119288</v>
+        <v>71.8488578017961</v>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>depot_arrival</t>
+          <t>departure</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="E26" t="n">
-        <v>587.9826663713962</v>
+        <v>436.1844374061087</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1616,7 +1621,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1627,19 +1632,23 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>587.9826663713962</v>
+        <v>935.9368411926835</v>
       </c>
       <c r="L26" t="n">
-        <v>2.83447493940356</v>
-      </c>
-      <c r="M26" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>backup</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>35.42442890089805</v>
+        <v>77.67339307890811</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1647,10 +1656,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="E27" t="n">
-        <v>125.2050337119815</v>
+        <v>216.2341291490647</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
@@ -1675,1821 +1684,9 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>-15.42442890089805</v>
+        <v>-36.67339307890811</v>
       </c>
       <c r="M27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>35.83669653945405</v>
-      </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>77</v>
-      </c>
-      <c r="E28" t="n">
-        <v>120.4397153328737</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>-15.83669653945405</v>
-      </c>
-      <c r="M28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>37.92442890089805</v>
-      </c>
-      <c r="B29" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>54</v>
-      </c>
-      <c r="E29" t="n">
-        <v>125.2050337119815</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>-17.92442890089805</v>
-      </c>
-      <c r="M29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>38.83669653945405</v>
-      </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>77</v>
-      </c>
-      <c r="E30" t="n">
-        <v>120.4397153328737</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>-18.83669653945405</v>
-      </c>
-      <c r="M30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>40.4138126514911</v>
-      </c>
-      <c r="B31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>arrival</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>37</v>
-      </c>
-      <c r="E31" t="n">
-        <v>453.352229457777</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>453.352229457777</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>13.91723746970178</v>
-      </c>
-      <c r="M31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>40.42442890089805</v>
-      </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>54</v>
-      </c>
-      <c r="E32" t="n">
-        <v>312.722774499836</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>-20.42442890089805</v>
-      </c>
-      <c r="M32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>41.83669653945405</v>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>77</v>
-      </c>
-      <c r="E33" t="n">
-        <v>325.8921211245685</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>-21.83669653945405</v>
-      </c>
-      <c r="M33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>42.92442890089805</v>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>54</v>
-      </c>
-      <c r="E34" t="n">
-        <v>312.722774499836</v>
-      </c>
-      <c r="F34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>-22.92442890089805</v>
-      </c>
-      <c r="M34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>44.83669653945405</v>
-      </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>77</v>
-      </c>
-      <c r="E35" t="n">
-        <v>325.8921211245685</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>-24.83669653945405</v>
-      </c>
-      <c r="M35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>45.4138126514911</v>
-      </c>
-      <c r="B36" t="n">
-        <v>2</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>departure</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>37</v>
-      </c>
-      <c r="E36" t="n">
-        <v>453.352229457777</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>453.352229457777</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>8.917237469701782</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>backup</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>45.42442890089805</v>
-      </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>54</v>
-      </c>
-      <c r="E37" t="n">
-        <v>312.722774499836</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>-25.42442890089805</v>
-      </c>
-      <c r="M37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>47.83669653945405</v>
-      </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>77</v>
-      </c>
-      <c r="E38" t="n">
-        <v>325.8921211245685</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>-27.83669653945405</v>
-      </c>
-      <c r="M38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>47.92442890089805</v>
-      </c>
-      <c r="B39" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>54</v>
-      </c>
-      <c r="E39" t="n">
-        <v>312.722774499836</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>-27.92442890089805</v>
-      </c>
-      <c r="M39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>50.42442890089805</v>
-      </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>54</v>
-      </c>
-      <c r="E40" t="n">
-        <v>312.722774499836</v>
-      </c>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>-30.42442890089805</v>
-      </c>
-      <c r="M40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>50.83669653945405</v>
-      </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>77</v>
-      </c>
-      <c r="E41" t="n">
-        <v>325.8921211245685</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>-30.83669653945405</v>
-      </c>
-      <c r="M41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>51.49657518178932</v>
-      </c>
-      <c r="B42" t="n">
-        <v>2</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>depot_arrival</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>37</v>
-      </c>
-      <c r="E42" t="n">
-        <v>453.352229457777</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>453.352229457777</v>
-      </c>
-      <c r="L42" t="n">
-        <v>2.834474939403563</v>
-      </c>
-      <c r="M42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>52.92442890089805</v>
-      </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>54</v>
-      </c>
-      <c r="E43" t="n">
-        <v>312.722774499836</v>
-      </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>-32.92442890089805</v>
-      </c>
-      <c r="M43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>53.83669653945405</v>
-      </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>77</v>
-      </c>
-      <c r="E44" t="n">
-        <v>325.8921211245685</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>-33.83669653945405</v>
-      </c>
-      <c r="M44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>55.42442890089805</v>
-      </c>
-      <c r="B45" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>54</v>
-      </c>
-      <c r="E45" t="n">
-        <v>312.722774499836</v>
-      </c>
-      <c r="F45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>-35.42442890089805</v>
-      </c>
-      <c r="M45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>56.83669653945405</v>
-      </c>
-      <c r="B46" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>77</v>
-      </c>
-      <c r="E46" t="n">
-        <v>325.8921211245685</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>-36.83669653945405</v>
-      </c>
-      <c r="M46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>57.57933771208754</v>
-      </c>
-      <c r="B47" t="n">
-        <v>2</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>arrival</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>37</v>
-      </c>
-      <c r="E47" t="n">
-        <v>453.352229457777</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H47" t="n">
-        <v>1</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J47" t="n">
-        <v>453.352229457777</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>13.91723746970178</v>
-      </c>
-      <c r="M47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>57.92442890089805</v>
-      </c>
-      <c r="B48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>54</v>
-      </c>
-      <c r="E48" t="n">
-        <v>312.722774499836</v>
-      </c>
-      <c r="F48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>1</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>-37.92442890089805</v>
-      </c>
-      <c r="M48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>59.83669653945405</v>
-      </c>
-      <c r="B49" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>77</v>
-      </c>
-      <c r="E49" t="n">
-        <v>325.8921211245685</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
-        <v>1</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>-39.83669653945405</v>
-      </c>
-      <c r="M49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>60.42442890089805</v>
-      </c>
-      <c r="B50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>54</v>
-      </c>
-      <c r="E50" t="n">
-        <v>102.4881591779526</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>1</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>-40.42442890089805</v>
-      </c>
-      <c r="M50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>62.57933771208754</v>
-      </c>
-      <c r="B51" t="n">
-        <v>2</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>departure</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>37</v>
-      </c>
-      <c r="E51" t="n">
-        <v>417.9917713727622</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>453.352229457777</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>8.917237469701782</v>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>backup</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>62.83669653945405</v>
-      </c>
-      <c r="B52" t="n">
-        <v>0</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>77</v>
-      </c>
-      <c r="E52" t="n">
-        <v>514.330148794661</v>
-      </c>
-      <c r="F52" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>1</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>-42.83669653945405</v>
-      </c>
-      <c r="M52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>62.92442890089805</v>
-      </c>
-      <c r="B53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>54</v>
-      </c>
-      <c r="E53" t="n">
-        <v>102.4881591779526</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>1</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>-42.92442890089805</v>
-      </c>
-      <c r="M53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>65.42442890089805</v>
-      </c>
-      <c r="B54" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>54</v>
-      </c>
-      <c r="E54" t="n">
-        <v>102.4881591779526</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>1</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>-45.42442890089805</v>
-      </c>
-      <c r="M54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>65.83669653945405</v>
-      </c>
-      <c r="B55" t="n">
-        <v>0</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>77</v>
-      </c>
-      <c r="E55" t="n">
-        <v>514.330148794661</v>
-      </c>
-      <c r="F55" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H55" t="n">
-        <v>1</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>-45.83669653945405</v>
-      </c>
-      <c r="M55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>67.92442890089805</v>
-      </c>
-      <c r="B56" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>54</v>
-      </c>
-      <c r="E56" t="n">
-        <v>102.4881591779526</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
-        <v>1</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>-47.92442890089805</v>
-      </c>
-      <c r="M56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>68.66210024238576</v>
-      </c>
-      <c r="B57" t="n">
-        <v>2</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>depot_arrival</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>37</v>
-      </c>
-      <c r="E57" t="n">
-        <v>417.9917713727622</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>453.352229457777</v>
-      </c>
-      <c r="L57" t="n">
-        <v>2.834474939403556</v>
-      </c>
-      <c r="M57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>68.83669653945405</v>
-      </c>
-      <c r="B58" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>77</v>
-      </c>
-      <c r="E58" t="n">
-        <v>514.330148794661</v>
-      </c>
-      <c r="F58" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H58" t="n">
-        <v>1</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>-48.83669653945405</v>
-      </c>
-      <c r="M58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>70.42442890089805</v>
-      </c>
-      <c r="B59" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>54</v>
-      </c>
-      <c r="E59" t="n">
-        <v>102.4881591779526</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>1</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>-50.42442890089805</v>
-      </c>
-      <c r="M59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>71.83669653945405</v>
-      </c>
-      <c r="B60" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>77</v>
-      </c>
-      <c r="E60" t="n">
-        <v>514.330148794661</v>
-      </c>
-      <c r="F60" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H60" t="n">
-        <v>1</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>-51.83669653945405</v>
-      </c>
-      <c r="M60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>72.92442890089805</v>
-      </c>
-      <c r="B61" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>54</v>
-      </c>
-      <c r="E61" t="n">
-        <v>102.4881591779526</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
-        <v>1</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>-52.92442890089805</v>
-      </c>
-      <c r="M61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>74.74486277268399</v>
-      </c>
-      <c r="B62" t="n">
-        <v>2</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>arrival</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>37</v>
-      </c>
-      <c r="E62" t="n">
-        <v>417.9917713727622</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H62" t="n">
-        <v>1</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
-        <v>417.9917713727622</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>13.91723746970177</v>
-      </c>
-      <c r="M62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>74.83669653945405</v>
-      </c>
-      <c r="B63" t="n">
-        <v>0</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>77</v>
-      </c>
-      <c r="E63" t="n">
-        <v>514.330148794661</v>
-      </c>
-      <c r="F63" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H63" t="n">
-        <v>1</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>-54.83669653945405</v>
-      </c>
-      <c r="M63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>75.42442890089805</v>
-      </c>
-      <c r="B64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>54</v>
-      </c>
-      <c r="E64" t="n">
-        <v>102.4881591779526</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H64" t="n">
-        <v>1</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>-55.42442890089805</v>
-      </c>
-      <c r="M64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>77.83669653945405</v>
-      </c>
-      <c r="B65" t="n">
-        <v>0</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>77</v>
-      </c>
-      <c r="E65" t="n">
-        <v>514.330148794661</v>
-      </c>
-      <c r="F65" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H65" t="n">
-        <v>1</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>-57.83669653945405</v>
-      </c>
-      <c r="M65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>77.92442890089805</v>
-      </c>
-      <c r="B66" t="n">
-        <v>1</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>crash</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>54</v>
-      </c>
-      <c r="E66" t="n">
-        <v>102.4881591779526</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="H66" t="n">
-        <v>1</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>-57.92442890089805</v>
-      </c>
-      <c r="M66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>79.74486277268399</v>
-      </c>
-      <c r="B67" t="n">
-        <v>2</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>departure</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>37</v>
-      </c>
-      <c r="E67" t="n">
-        <v>417.9917713727622</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="H67" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J67" t="n">
-        <v>417.9917713727622</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>8.917237469701774</v>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>backup</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3502,7 +1699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3518,7 +1715,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>waypoint_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3663,7 +1860,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>revenue</t>
+          <t>risk</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -3675,10 +1872,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>104.0104123984499</v>
+        <v>327.9763458157603</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3687,7 +1884,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>revenue</t>
+          <t>risk</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -3699,7 +1896,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>125.2050337119815</v>
+        <v>448.9299082816925</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -3711,7 +1908,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>revenue</t>
+          <t>risk</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -3723,7 +1920,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>587.9826663713962</v>
+        <v>114.1270985852852</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -3735,7 +1932,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>revenue</t>
+          <t>risk</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -3747,7 +1944,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>120.4397153328737</v>
+        <v>334.820610868813</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -3759,7 +1956,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>revenue</t>
+          <t>risk</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -3771,7 +1968,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>146.1529120578085</v>
+        <v>515.2593816132376</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -3779,11 +1976,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>risk</t>
+          <t>revenue</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -3795,7 +1992,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>104.0104123984499</v>
+        <v>452.9450791042515</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -3803,11 +2000,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>risk</t>
+          <t>revenue</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -3819,7 +2016,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>125.2050337119815</v>
+        <v>296.982854685588</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -3827,11 +2024,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>risk</t>
+          <t>revenue</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3843,7 +2040,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>587.9826663713962</v>
+        <v>292.9497807222561</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -3851,11 +2048,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>risk</t>
+          <t>revenue</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3867,7 +2064,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>120.4397153328737</v>
+        <v>557.7764995445606</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -3875,11 +2072,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>risk</t>
+          <t>revenue</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3891,10 +2088,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>146.1529120578085</v>
+        <v>359.9985069829038</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3903,7 +2100,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>revenue</t>
+          <t>risk</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3915,7 +2112,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>182.4648242307073</v>
+        <v>452.9450791042515</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -3927,7 +2124,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>revenue</t>
+          <t>risk</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3939,10 +2136,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>312.722774499836</v>
+        <v>296.982854685588</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3951,7 +2148,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>revenue</t>
+          <t>risk</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3963,10 +2160,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>453.352229457777</v>
+        <v>292.9497807222561</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -3975,7 +2172,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>revenue</t>
+          <t>risk</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3987,10 +2184,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>325.8921211245685</v>
+        <v>557.7764995445606</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -3999,7 +2196,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>revenue</t>
+          <t>risk</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -4011,7 +2208,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>348.7065081279904</v>
+        <v>359.9985069829038</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -4019,11 +2216,11 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>risk</t>
+          <t>revenue</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -4035,19 +2232,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>182.4648242307073</v>
+        <v>150.4403927080818</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>risk</t>
+          <t>revenue</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4059,7 +2256,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>312.722774499836</v>
+        <v>499.7524037865747</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -4067,11 +2264,11 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>risk</t>
+          <t>revenue</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -4083,19 +2280,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>453.352229457777</v>
+        <v>458.7130105615833</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>risk</t>
+          <t>revenue</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4107,7 +2304,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>325.8921211245685</v>
+        <v>367.0019058214374</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -4115,11 +2312,11 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>risk</t>
+          <t>revenue</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -4131,10 +2328,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>348.7065081279904</v>
+        <v>370.8752724862744</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -4143,7 +2340,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>revenue</t>
+          <t>risk</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -4155,10 +2352,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>215.7412205481398</v>
+        <v>150.4403927080818</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -4167,7 +2364,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>revenue</t>
+          <t>risk</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -4179,10 +2376,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102.4881591779526</v>
+        <v>499.7524037865747</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -4191,7 +2388,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>revenue</t>
+          <t>risk</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -4203,7 +2400,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>417.9917713727622</v>
+        <v>458.7130105615833</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4215,7 +2412,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>revenue</t>
+          <t>risk</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4227,7 +2424,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>514.330148794661</v>
+        <v>367.0019058214374</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
@@ -4239,7 +2436,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>revenue</t>
+          <t>risk</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4251,15 +2448,15 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>216.2341291490647</v>
+        <v>370.8752724862744</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4275,15 +2472,15 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>436.1844374061087</v>
+        <v>102.4881591779526</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4299,15 +2496,15 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>488.3860991704668</v>
+        <v>417.9917713727622</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4323,7 +2520,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>64.92311074473967</v>
+        <v>514.330148794661</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4331,7 +2528,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4347,7 +2544,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>157.275583599488</v>
+        <v>216.2341291490647</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
@@ -4355,7 +2552,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4371,9 +2568,129 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>147.9687471631378</v>
+        <v>436.1844374061087</v>
       </c>
       <c r="F36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>80</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>risk</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>19</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>(5, 35)</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>102.4881591779526</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>80</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>risk</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>54</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>(20, 15)</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>417.9917713727622</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>80</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>risk</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>37</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>(10, 60)</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>514.330148794661</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>80</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>risk</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>77</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>(30, 0)</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>216.2341291490647</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>80</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>risk</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>60</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>(20, 45)</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>436.1844374061087</v>
+      </c>
+      <c r="F41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4388,6 +2705,208 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>uav_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sequence</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sequence_length</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>m_j</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>total_distance</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>estimated_cycle_time</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>max_flight_time</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>crash_count</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>completed_missions</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>delivered_revenue</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>total_backed_up_revenue</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>final_status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>[77, 19]</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>108.3669653945405</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.67339307890811</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41</v>
+      </c>
+      <c r="H2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>787.7656899730645</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>crashed_and_replaced</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>[54, 60]</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>104.2442890089805</v>
+      </c>
+      <c r="F3" t="n">
+        <v>40.84885780179611</v>
+      </c>
+      <c r="G3" t="n">
+        <v>41</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>808.9284152645962</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1744.86525645728</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>[37]</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>121.6552506059644</v>
+      </c>
+      <c r="F4" t="n">
+        <v>34.33105012119288</v>
+      </c>
+      <c r="G4" t="n">
+        <v>41</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>572.8401091468686</v>
+      </c>
+      <c r="K4" t="n">
+        <v>572.8401091468686</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -4445,34 +2964,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" t="n">
-        <v>44</v>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4</v>
-      </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>3653.792241824501</v>
+        <v>3105.471055577213</v>
       </c>
       <c r="I2" t="n">
-        <v>1912.678896659713</v>
+        <v>3105.471055577213</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
